--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40A.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="86">
   <si>
     <t>49010</t>
   </si>
@@ -143,6 +143,136 @@
   </si>
   <si>
     <t>s/n</t>
+  </si>
+  <si>
+    <t>C36AEAED796DFAAEE04F83F5884A6E3F</t>
+  </si>
+  <si>
+    <t>01/04/2022</t>
+  </si>
+  <si>
+    <t>30/06/2022</t>
+  </si>
+  <si>
+    <t>Fondo de Aportaciones Múltiples (FAM) 2019</t>
+  </si>
+  <si>
+    <t>Evaluación de Consistencia y Resultados del Fondo de
+Aportaciones Múltiples (FAM), ejercicio fiscal 2019</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/portal/assets/archivos/pdf/evaluaciones_externas/NOTIFICACI%C3%93N_DE_CUMPLIMIENTO_EVALUACI%C3%93N_PAE.pdf</t>
+  </si>
+  <si>
+    <t>15/07/2022</t>
+  </si>
+  <si>
+    <t>En el periodo del 01 de abril de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, no reportará ninguna evaluación a programas financiados con recursos públicos, sin embargo, si hubiera alguna evaluación a algún programa, se hará la actualización y validación dentro de los 15 días posteriores a la evaluación.</t>
+  </si>
+  <si>
+    <t>792B1C60AC35DCFD67E3CC0BA34D12D5</t>
+  </si>
+  <si>
+    <t>Fondo de Aportaciones Múltiples (FAM) 2018</t>
+  </si>
+  <si>
+    <t>Evaluación de Procesos    Ejercicio fiscal 2018</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/portal/evaluaciones_externas/index-FAM.html#</t>
+  </si>
+  <si>
+    <t>15DB79C7E7E9E2BA770EE141C7E12B04</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>546503BF8D1142520BC0ED865B057137</t>
+  </si>
+  <si>
+    <t>31/03/2022</t>
+  </si>
+  <si>
+    <t>Fondo de aportaiones multiples (FAM) infraestructura educacion media superior.</t>
+  </si>
+  <si>
+    <t>indicadores</t>
+  </si>
+  <si>
+    <t>https://cgpi.tlaxcala.gob.mx/index.php/evaluacion/pae-2022</t>
+  </si>
+  <si>
+    <t>03/05/2022</t>
+  </si>
+  <si>
+    <t>En el periodo del 01 de enero de 2022 al 31 de marzo de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, no reportará ninguna evaluación a programas financiados con recursos públicos, sin embargo, si hubiera alguna evaluación a algún programa, se hará la actualización y validación dentro de los 15 días posteriores a la evaluación.</t>
+  </si>
+  <si>
+    <t>BE6BBD614C42307F</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>01/07/2021</t>
+  </si>
+  <si>
+    <t>30/09/2021</t>
+  </si>
+  <si>
+    <t>26/10/2021</t>
+  </si>
+  <si>
+    <t>En el periodo del 01 de julio de 2021 al 30 de septiembre de 2021, el Colegio de Bachilleres del Estado de Tlaxcala, no reportará ninguna evaluación a programas financiados con recursos públicos, sin embargo, si hubiera alguna evaluación a algún programa, se hará la actualización y validación dentro de los 15 días posteriores a la evaluación.</t>
+  </si>
+  <si>
+    <t>FDB2F537E3335661</t>
+  </si>
+  <si>
+    <t>2EEA59EFBE750D78</t>
+  </si>
+  <si>
+    <t>A1CAAE90EA7765F3</t>
+  </si>
+  <si>
+    <t>01/04/2021</t>
+  </si>
+  <si>
+    <t>30/06/2021</t>
+  </si>
+  <si>
+    <t>15/07/2021</t>
+  </si>
+  <si>
+    <t>En el periodo del 01 de abril de 2021 al 30 de junio de 2021, el Colegio de Bachilleres del Estado de Tlaxcala, no reportará ninguna evaluación a programas financiados con recursos públicos, sin embargo, si hubiera alguna evaluación a algún programa, se hará la actualización y validación dentro de los 15 días posteriores a la evaluación.</t>
+  </si>
+  <si>
+    <t>DAAD399ADA5A108E</t>
+  </si>
+  <si>
+    <t>297214727085FEC2</t>
+  </si>
+  <si>
+    <t>01/01/2021</t>
+  </si>
+  <si>
+    <t>31/03/2021</t>
+  </si>
+  <si>
+    <t>29/04/2021</t>
+  </si>
+  <si>
+    <t>En el periodo del 01 de enero de 2021 al 31 de marzo de 2021, el Colegio de Bachilleres del Estado de Tlaxcala, no reportará ninguna evaluación a programas financiados con recursos públicos, sin embargo, si hubiera alguna evaluación a algún programa, se hará la actualización y validación dentro de los 15 días posteriores a la evaluación.</t>
+  </si>
+  <si>
+    <t>C3DE1667E52F0AB0</t>
+  </si>
+  <si>
+    <t>20183DF50922A496</t>
+  </si>
+  <si>
+    <t>8B8E7D076070D640</t>
   </si>
 </sst>
 </file>
@@ -535,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
@@ -734,6 +864,461 @@
         <v>42</v>
       </c>
     </row>
+    <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A6:K6"/>
